--- a/agent_runs/manjidiwang/episodes/ep01/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep01/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>酒店惊变 （，总时长：13秒，镜头数：5个）</t>
+          <t>酒店惊变</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>阴谋揭露 （，总时长：10秒，镜头数：5个）</t>
+          <t>阴谋揭露</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>妹妹递酒 （，总时长：10秒，镜头数：5个）</t>
+          <t>妹妹递酒</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>苏家密谋 （，总时长：11秒，镜头数：5个）</t>
+          <t>苏家密谋</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>利益筹码 （，总时长：10秒，镜头数：5个）</t>
+          <t>利益筹码</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>威逼利诱 （，总时长：10秒，镜头数：5个）</t>
+          <t>威逼利诱</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>联姻破局 （，总时长：10秒，镜头数：5个）</t>
+          <t>联姻破局</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>破门而入 （，总时长：11秒，镜头数：5个）</t>
+          <t>破门而入</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>步步紧逼 （，总时长：12秒，镜头数：6个）</t>
+          <t>步步紧逼</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>权势碾压 （，总时长：14秒，镜头数：7个）</t>
+          <t>权势碾压</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>逐客令 （，总时长：10秒，镜头数：4个）</t>
+          <t>逐客令</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>真实身份 （，总时长：10秒，镜头数：5个）</t>
+          <t>真实身份</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>废柴人设 （，总时长：11秒，镜头数：5个）</t>
+          <t>废柴人设</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>利刃与弃子 （，总时长：14秒，镜头数：5个）</t>
+          <t>利刃与弃子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>转身离去 （，总时长：11秒，镜头数：3个）</t>
+          <t>转身离去</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>父子通话 （，总时长：12秒，镜头数：6个）</t>
+          <t>父子通话</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>危机暂缓 （，总时长：10秒，镜头数：5个）</t>
+          <t>危机暂缓</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>驱车离去 （，总时长：10秒，镜头数：4个）</t>
+          <t>驱车离去</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>前世闪回 （，总时长：14秒，镜头数：6个）</t>
+          <t>前世闪回</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>重生誓约 （，总时长：12秒，镜头数：4个）</t>
+          <t>重生誓约</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
